--- a/Uppdrag.xlsx
+++ b/Uppdrag.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\GRF Resursteamet\JOURNAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://borasstad-my.sharepoint.com/personal/henric_bergqvist_edu_boras_se/Documents/UPPDRAG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C348B5-0078-48B1-B18E-DAC8C746399E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{BC7EC585-C4F2-4C05-B70C-164A18EA1FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BB611F5-AA74-4C4D-A4BE-18AE2020480C}"/>
   <bookViews>
-    <workbookView xWindow="12600" yWindow="10" windowWidth="13070" windowHeight="13670" xr2:uid="{2DDCA28D-8E74-4114-9109-23716460B380}"/>
+    <workbookView xWindow="12000" yWindow="130" windowWidth="13410" windowHeight="13100" xr2:uid="{2DDCA28D-8E74-4114-9109-23716460B380}"/>
   </bookViews>
   <sheets>
     <sheet name="UPPDRAG" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="114">
   <si>
     <t>SKOLA</t>
   </si>
@@ -389,6 +389,33 @@
   </si>
   <si>
     <t>Handledning</t>
+  </si>
+  <si>
+    <t>Dalsjöskolan 7-9</t>
+  </si>
+  <si>
+    <t>rektor kommer att höra av sig</t>
+  </si>
+  <si>
+    <t>tidigare elev avstängd. Hemundervisning</t>
+  </si>
+  <si>
+    <t>Kolumn21</t>
+  </si>
+  <si>
+    <t>Ansv. Edagog</t>
+  </si>
+  <si>
+    <t>RT_PEDAGOG</t>
+  </si>
+  <si>
+    <t>AVSLUT</t>
+  </si>
+  <si>
+    <t>Dalsjöskolan 4-6</t>
+  </si>
+  <si>
+    <t>Love</t>
   </si>
 </sst>
 </file>
@@ -922,6 +949,40 @@
 </FeaturePropertyBags>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{88EF73F4-61DB-411C-A19C-2FDA69E7029E}" name="UppdargTabell" displayName="UppdargTabell" ref="A2:U100" totalsRowShown="0">
+  <autoFilter ref="A2:U100" xr:uid="{88EF73F4-61DB-411C-A19C-2FDA69E7029E}"/>
+  <tableColumns count="21">
+    <tableColumn id="1" xr3:uid="{42A169AC-B449-4C2D-A461-4BAFB5F43AFB}" name="SKOLA"/>
+    <tableColumn id="2" xr3:uid="{34865510-CBF0-41AC-BEEA-1D59EEB241F4}" name="ELEV"/>
+    <tableColumn id="3" xr3:uid="{587D65FD-94BB-4638-A7BA-79BB993C86B1}" name="Årsk."/>
+    <tableColumn id="4" xr3:uid="{1262225C-4D79-4CAA-8AAA-74F83A704C9E}" name="UPPDRAGSBESKRIVNING"/>
+    <tableColumn id="5" xr3:uid="{12CAF086-9BDF-4B71-BE55-7913B48E92B6}" name="PRN"/>
+    <tableColumn id="6" xr3:uid="{AE88D87A-DAB9-48E7-B117-B290A7079F68}" name="UPPDRAGSANSÖKAN"/>
+    <tableColumn id="7" xr3:uid="{56DB26F3-3D90-4C58-B0D3-1938563993C1}" name="INSKRIVN."/>
+    <tableColumn id="8" xr3:uid="{B3FFDCFD-B685-4403-B578-27ADC01D43FE}" name="SKOLSKJUTS"/>
+    <tableColumn id="9" xr3:uid="{99C695C5-7DA3-4FB4-BAC2-925BD673EDF4}" name="BESÖK INFÖR"/>
+    <tableColumn id="10" xr3:uid="{AB12CB27-833F-439E-82C4-CA52BC6AD707}" name="SKOLMTRL"/>
+    <tableColumn id="11" xr3:uid="{1F1FB7DE-7EF5-45C9-9C4C-D56779A9EBD0}" name="Ansv. Edagog"/>
+    <tableColumn id="12" xr3:uid="{BEC87887-6EDA-4B02-8BA6-B0CB9EC5E7AC}" name="RT_PEDAGOG"/>
+    <tableColumn id="13" xr3:uid="{5E4FFC73-EE7C-4377-96EF-C18CC257D5DF}" name="KOST"/>
+    <tableColumn id="14" xr3:uid="{8EC2298E-2FE3-44BD-946F-E547AC1DBB11}" name="START"/>
+    <tableColumn id="15" xr3:uid="{1F1C74EB-9458-48AB-ACEF-B21D3752A562}" name="SLUT"/>
+    <tableColumn id="16" xr3:uid="{5769E903-2B6F-41F6-905D-F61CE010CF03}" name="PRIO"/>
+    <tableColumn id="17" xr3:uid="{B4F3959B-D7D9-42F8-B3C1-59B0C419A31A}" name="ANSVARIG"/>
+    <tableColumn id="18" xr3:uid="{82BC3EBE-ED8A-4BCC-ABD7-DE336C0C54CE}" name="ÖVRIGT"/>
+    <tableColumn id="19" xr3:uid="{ADC1B478-7DAC-4BE0-A789-C30D2747B927}" name="AVSLUT"/>
+    <tableColumn id="20" xr3:uid="{A824DF4F-8118-4687-B94E-0A2B6678D8CB}" name="Uppföljningsdatum"/>
+    <tableColumn id="21" xr3:uid="{A4D89FB0-0A58-45FE-857F-5DE2FDEBA424}" name="Kolumn21"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-tema">
   <a:themeElements>
@@ -1243,7 +1304,9 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.453125" customWidth="1"/>
     <col min="4" max="4" width="24.08984375" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
     <col min="7" max="7" width="11.54296875" customWidth="1"/>
     <col min="8" max="8" width="13.7265625" customWidth="1"/>
@@ -1251,13 +1314,79 @@
     <col min="10" max="10" width="12.08984375" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
     <col min="12" max="12" width="14.26953125" customWidth="1"/>
-    <col min="14" max="15" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="11.54296875" customWidth="1"/>
     <col min="17" max="17" width="11.7265625" customWidth="1"/>
     <col min="18" max="18" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.54296875" customWidth="1"/>
     <col min="20" max="20" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" t="s">
+        <v>109</v>
+      </c>
+      <c r="L2" t="s">
+        <v>110</v>
+      </c>
+      <c r="M2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S2" t="s">
+        <v>111</v>
+      </c>
+      <c r="T2" t="s">
+        <v>103</v>
+      </c>
+      <c r="U2" t="s">
+        <v>108</v>
+      </c>
+    </row>
     <row r="3" spans="1:30" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="24" t="s">
         <v>0</v>
@@ -1655,7 +1784,7 @@
       <c r="T9" s="55"/>
       <c r="U9" s="44"/>
       <c r="W9" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.35">
@@ -1708,6 +1837,9 @@
       </c>
       <c r="T10" s="56"/>
       <c r="U10" s="43"/>
+      <c r="W10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A11" s="48" t="s">
@@ -2416,10 +2548,14 @@
       <c r="T25" s="55"/>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A26" s="49"/>
+      <c r="A26" s="49" t="s">
+        <v>105</v>
+      </c>
       <c r="B26" s="39"/>
       <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
+      <c r="D26" s="39" t="s">
+        <v>60</v>
+      </c>
       <c r="E26" s="40" t="b">
         <v>0</v>
       </c>
@@ -2441,21 +2577,29 @@
       <c r="M26" s="40" t="b">
         <v>0</v>
       </c>
-      <c r="N26" s="39"/>
+      <c r="N26" s="42">
+        <v>46265</v>
+      </c>
       <c r="O26" s="39"/>
       <c r="P26" s="39"/>
       <c r="Q26" s="39"/>
-      <c r="R26" s="39"/>
+      <c r="R26" s="39" t="s">
+        <v>106</v>
+      </c>
       <c r="S26" s="40" t="b">
         <v>0</v>
       </c>
       <c r="T26" s="56"/>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A27" s="48"/>
+      <c r="A27" s="48" t="s">
+        <v>19</v>
+      </c>
       <c r="B27" s="36"/>
       <c r="C27" s="36"/>
-      <c r="D27" s="39"/>
+      <c r="D27" s="39" t="s">
+        <v>60</v>
+      </c>
       <c r="E27" s="37" t="b">
         <v>0</v>
       </c>
@@ -2477,21 +2621,31 @@
       <c r="M27" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="N27" s="36"/>
+      <c r="N27" s="38">
+        <v>46265</v>
+      </c>
       <c r="O27" s="36"/>
       <c r="P27" s="36"/>
       <c r="Q27" s="36"/>
-      <c r="R27" s="36"/>
+      <c r="R27" s="36" t="s">
+        <v>107</v>
+      </c>
       <c r="S27" s="33" t="b">
         <v>0</v>
       </c>
       <c r="T27" s="55"/>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A28" s="49"/>
-      <c r="B28" s="39"/>
+      <c r="A28" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>113</v>
+      </c>
       <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
+      <c r="D28" s="39" t="s">
+        <v>60</v>
+      </c>
       <c r="E28" s="40" t="b">
         <v>0</v>
       </c>
@@ -4291,7 +4445,7 @@
       <c r="A78" s="50"/>
       <c r="B78" s="51"/>
       <c r="C78" s="51"/>
-      <c r="D78" s="51"/>
+      <c r="D78" s="39"/>
       <c r="E78" s="52" t="b">
         <v>0</v>
       </c>
@@ -4352,13 +4506,16 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L7:L15 L25:L78" xr:uid="{0754396A-134C-4DE2-B54E-EF3865DBD9A3}">
       <formula1>$W$17:$W$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D26:D78" xr:uid="{874E0C58-A175-420B-9956-CE9B76DC367B}">
-      <formula1>$W$5:$W$9</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D26:D78" xr:uid="{6E848D83-9B5C-4672-AF12-CA19BE379712}">
+      <formula1>$W$5:$W$10</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
